--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_001/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_001/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -359,6 +364,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -434,11 +454,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -474,6 +489,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -545,11 +565,6 @@
       </text>
     </comment>
     <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1311,17 +1326,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>LCL-42 Avionics Cold Plate CHT Model</t>
+          <t>LCL-42 Avionics Cold Plate Thermal Model</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Predict peak junction temperature of LCL-42 power electronics under Max-Cruise to verify Tj ≤ 95 C with 95% confidence</t>
+          <t>Predict peak MOSFET junction temperature for LCL-42 cold plate under Max-Cruise conditions</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Steady-state conjugate heat transfer simulation of the LCL-42 1.2 kW power avionics cold plate on the LV-9R reusable launch vehicle. The model predicts MOSFET junction temperatures, inter-device temperature uniformity, and coolant pressure drop under the Max-Cruise environmental case (PAO-4 inlet 35 C, 1.0 L/min, bay air 45 C). Results support CDR and thermal margin certification. Uncertainty is quantified via Latin Hypercube Sampling with Gaussian process surrogate (N=200).</t>
+          <t>Conjugate heat transfer simulation of the LCL-42 1.2 kW power electronics module mounted to a liquid-cooled cold plate on the LV-9R vehicle. The model predicts peak junction temperature (Tj), temperature uniformity across phase legs, and coolant pressure drop under Max-Cruise environmental conditions (altitude 10.5 km, bay air 45 C, PAO-4 coolant at 35 C inlet, 1.0 L/min), including manufacturing and operating variability. Used to support CDR and thermal margin certification.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1351,7 +1366,7 @@
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>R. Zhao (Lead); M. Patel (Secondary); K. Nguyen (Thermal Test)</t>
+          <t>R. Zhao, Thermal/Fluids Analysis Group</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1359,9 +1374,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (Credibility Assessment Report: Conjugate Heat Transfer Model of the LCL-42 Avionics Cold Plate, Flight Systems Division, 2026-08-06)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1422,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1480,7 +1495,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Peak Junction Temperature Criterion</t>
+          <t>Peak Junction Temperature and Thermal Margin Requirement</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1490,7 +1505,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Peak MOSFET junction temperature Tj ≤ 95 C with 95% probability under Max-Cruise; inter-device uniformity ≤ 6 C on a phase leg; model prediction within ±8 C of thermal-rig measurements for validation configuration</t>
+          <t>Peak junction temperature Tj ≤ 95 C with 95% probability under Max-Cruise; any two MOSFET case temperatures on the same phase leg differ by ≤ 6 C; predicted peak Tj within ±8 C of thermal-rig test measurements for the validation configuration.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1512,12 +1527,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>LCL-42 Cold Plate CHT Model (Ansys Fluent 2023 R2)</t>
+          <t>LCL-42 CHT Ansys Fluent Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Steady-state (plus 200 s startup transient) conjugate heat transfer model: poly-hexcore coolant domain (14.7M cells) + conformal hexahedral solids (8.9M cells); SST k-ω turbulence; CAD from PDM rev LCL42_CP_A3; Dakota 6.16 + Gaussian process surrogate for UQ</t>
+          <t>Steady-state conjugate heat transfer model (plus 200 s startup transient) of the LCL-42 cold plate in Ansys Fluent 2023 R2, using SST k-omega turbulence, poly-hexcore mesh (16.5M cells medium), and Dakota-based LHS uncertainty quantification.</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1544,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Thermal Rig CP-VAL-07 Validation Dataset</t>
+          <t>CP-VAL-07 Thermal Rig Validation Data</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Five validation points (flow 0.8–1.2 L/min, inlet 30–40 C) with calibrated Type-K TCs (±0.4 C), IR camera, ultrasonic flow probe (±0.5%); raw DAQ and run logs archived in DataLake</t>
+          <t>Hardware thermal rig measurements for the LCL-42 cold plate at five (flow, inlet temperature) operating points; includes case temperatures, pressure drop, and flow maldistribution data with calibrated instrumentation.</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1566,24 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Manufacturer curve-fit data for PAO-4 viscosity and Cp (20–90 C); coupon compression tests (SiC-TIM-plate at 2 MPa) yielding TCC mean 20,000 W/m2-K, COV 30%; regression CI from tim_conductance_fit.ipynb</t>
+          <t>Manufacturer thermophysical property curves for PAO-4 coolant and coupon-level compression test data for TIM thermal contact conductance (mean 20,000 W/m2-K, COV 30%) used as model inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Electrical Power Budget and Component Heat Load Map</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Per-component electrical dissipation values for Max-Cruise duty case (MOSFETs 65 W each, gate drivers 3 W, DC/DC 22 W), cross-checked against PSU logs from the validation rig.</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2020,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Thermal Rig Validation — Case Temperature and Pressure Drop (5-point matrix)</t>
+          <t>Mesh Convergence and Richardson Extrapolation Study</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2003,12 +2035,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Model predictions of max device case temperature and channel pressure drop compared to rig CP-VAL-07 measurements across five (flow, inlet temperature) operating points; mean absolute deviation in case temperatures computed over all points</t>
+          <t>Three systematically refined meshes (Coarse 7.1M, Medium 16.5M, Fine 31.9M cells) used to assess discretization error for peak MOSFET junction temperature and total pressure drop using Richardson extrapolation and GCI.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Calibrated Type-K thermocouple and IR camera measurements; calibrated flow meter and pressure transducers</t>
+          <t>Richardson extrapolation estimate; observed order p ≈ 1.9 for temperature</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2018,12 +2050,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Measurement uncertainty (±0.6 C 95% CI on TC max); model form uncertainty σ_model = 2.0 C derived from five validation points</t>
+          <t>Richardson extrapolation, Grid Convergence Index (GCI95)</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Max case temp: model 80.9 C vs. test 82.3 ± 0.6 C (difference −1.4 C); mean absolute deviation 1.9 C across 5 points; ΔP: model 26.1 kPa vs. test 25.3 kPa (3.2% high); all within ±8 C acceptance criterion</t>
+          <t>GCI95 for peak Tj from Medium mesh = 1.4 C (0.9%); pressure drop GCI95 = 3.7%</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2035,7 +2067,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence and GCI Study</t>
+          <t>Code Verification Against Canonical Benchmark Problems</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2045,27 +2077,22 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (Coarse 7.1M, Medium 16.5M, Fine 31.9M cells) assessed for peak junction temperature and pressure drop using Richardson extrapolation and GCI95</t>
+          <t>Ansys Fluent conduction and convection modules exercised against 1D slab with convection boundary (analytical), fully developed turbulent pipe heat transfer (Gnielinski correlation), and two-material composite series resistance benchmark.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation extrapolated value; observed convergence order p ≈ 1.9</t>
+          <t>Analytical solutions and Gnielinski Nu correlation</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Grid Convergence Index (GCI95); Richardson extrapolation</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>GCI95 for peak Tj from Medium mesh = 1.4 C (0.9% of value); GCI95 for ΔP = 3.7%; energy balance: 0.41% Medium, 0.12% Fine</t>
+          <t>Reproduction within 0.7–2.2% on Fine mesh; conjugate interface error &lt; 1.5% on Medium mesh</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2077,7 +2104,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Code Verification — Canonical Benchmark Problems</t>
+          <t>Thermal Rig Hardware Validation (CP-VAL-07), Five Operating Points</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2087,22 +2114,27 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Ansys Fluent conduction and convection modules exercised against 1D slab with convection boundary (analytical), fully developed turbulent pipe heat transfer (Gnielinski correlation), and two-material composite conjugate interface with known series resistance</t>
+          <t>Model-predicted case temperatures and pressure drop compared to hardware rig measurements at five (flow rate, inlet temperature) combinations: (0.8/35), (1.0/35), (1.2/35), (1.0/30), (1.0/40) L/min and C. Max device case temperature, temperature spread across phase legs, and channel pressure drop compared.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Analytical solutions and Gnielinski Nu correlation</t>
+          <t>CP-VAL-07 rig measurements with calibrated thermocouples (±0.4 C), flow meter (±0.5%), RTD (±0.15 C)</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Measurement uncertainty propagation; model form uncertainty σ_model = 2.0 C derived from five validation points</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Analytical/Nu correlation reproduction within 0.7–2.2% on Fine mesh; conjugate interface error &lt; 1.5% on Medium mesh</t>
+          <t>Max Tc deviation −1.4 C (test 82.3 ± 0.6 C, model 80.9 C); mean absolute deviation across 5 points 1.9 C; ΔP 3.2% high; within ±8 C acceptance criterion</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2114,7 +2146,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Sampling UQ — Peak Junction Temperature Distribution</t>
+          <t>Uncertainty Quantification — Latin Hypercube Sampling with Gaussian Process Surrogate</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2124,12 +2156,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>200-sample LHS with Gaussian process surrogate (120 training runs, leave-one-out R2=0.995) propagating variability in TCC, MOSFET power, flow rate, inlet temperature, and channel width to peak Tj distribution</t>
+          <t>LHS (N=200) with Gaussian process surrogate (120 training runs, leave-one-out R2=0.995) propagating TCC, MOSFET power, flow rate, inlet temperature, and channel width variability to peak junction temperature distribution for Max-Cruise.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Acceptance threshold Tj ≤ 95 C with 95% probability</t>
+          <t>Acceptance threshold Tj ≤ 95 C at 95% confidence</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2139,12 +2171,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Sampling; Gaussian process surrogate; Sobol sensitivity indices</t>
+          <t>Latin Hypercube Sampling, Gaussian process surrogate, Sobol sensitivity indices</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>P(Tj &lt; 95 C) = 98.3%; 95th percentile Tj = 92.6 C (2.4 C margin); 99th percentile = 94.8 C; top Sobol index: TCC = 0.42</t>
+          <t>P(Tj &lt; 95 C) = 98.3%; 95th percentile Tj = 92.6 C; 99th percentile Tj = 94.8 C; 2.4 C margin to 95 C limit</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2156,7 +2188,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Outlet Temperature and Local Wall Temperature Comparison (Appendix G)</t>
+          <t>Time-Step Independence Study for 200 s Startup Transient</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2166,27 +2198,22 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Additional validation observables — coolant outlet temperature and local wall temperatures at three channel turns compared to rig IR readings; flow maldistribution across parallel branches compared to ultrasonic probe</t>
+          <t>Startup transient assessed at two time steps (1.0 s and 0.5 s, BDF2) to verify time-step independence of peak temperature overshoot prediction.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>IR camera readings (after emissivity correction); ultrasonic flow probe</t>
+          <t>Finer time step solution (0.5 s)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Measurement uncertainty propagation; IR emissivity correction uncertainty ±0.02</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Outlet temp: model 37.4 C vs. rig 37.6 ± 0.2 C; local wall temps within 0.9–1.6 C of IR; flow maldistribution &lt; 4% model, confirmed within measurement limits</t>
+          <t>Peak overshoot difference &lt; 0.5 C between 1.0 s and 0.5 s steps</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2340,12 +2367,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; in-house acceptance tests; custom code unit tested; postprocessing scripts with coverage metrics</t>
+          <t>Commercial solver with documented QA; in-house acceptance tests; version-controlled scripts with test coverage</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 is a COTS solver relied upon with vendor QA. In-house acceptance tests against canonical benchmarks performed. No custom UDFs except a property table reader that was unit tested. Postprocessing scripts have pytest coverage of 82%. Docker container archived to Artifactory for reproducibility. Runs reproduced on two clusters within 0.02 C (report.md Sections 4, 11).</t>
+          <t>Ansys Fluent 2023 R2 is COTS with vendor QA. In-house acceptance tests performed (canonical benchmarks). No custom UDFs except a property table reader that is unit tested. Post-processing scripts have pytest coverage at 82%. Docker container with full software stack archived to Artifactory for reproducibility. Runs on two hardware platforms yield results within 0.02 C and 1 Pa. Analyst training records maintained in LMS (latest completions 2025-11-03 and 2026-03-21).</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2374,12 +2401,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Reproduction of analytical solutions and established correlations within accepted tolerances</t>
+          <t>Reproduction of analytical solutions and recognized correlations within accepted tolerances for all relevant physics modules</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Fluent conduction and convection modules verified against: 1D slab analytical solution, Gnielinski turbulent pipe Nu correlation, two-material composite conjugate interface with known resistance. Errors 0.7–2.2% on Fine mesh, &lt; 1.5% for conjugate interface. Energy balance closes within 0.12% on Fine mesh (report.md Section 4).</t>
+          <t>Fluent conduction module verified against 1D slab analytical solution; convection module against Gnielinski fully-developed turbulent pipe correlation (0.7–2.2% on Fine mesh); conjugate interface verified against two-material series resistance (&lt; 1.5% on Medium mesh). Energy balance closes within 0.12% (Fine mesh). Cross-platform repeatability confirmed. Prior use on Pathfinder cold plate with flight telemetry correlation also supports code credibility.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2408,12 +2435,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>GCI95 &lt; 2 C for peak Tj; demonstrated convergence order near theoretical</t>
+          <t>GCI95 for peak Tj below thermal margin threshold; observed convergence order consistent with second-order scheme</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three meshes (7.1M, 16.5M, 31.9M cells) used with Richardson extrapolation. Observed order p ≈ 1.9 for peak Tj. GCI95 from Medium mesh: 1.4 C (0.9%) for Tj, 3.7% for ΔP. Time-step independence for transient: &lt; 0.5 C between 1.0 s and 0.5 s steps. Local manifold refinement confirmed y+ &lt; 1 throughout after peer review action A2 (report.md Sections 3, 4; appendix.md Appendix K).</t>
+          <t>Three systematically refined meshes (Coarse 7.1M, Medium 16.5M, Fine 31.9M). Richardson extrapolation yields observed order p ≈ 1.9 (consistent with second-order schemes). GCI95 from Medium mesh for peak Tj = 1.4 C (0.9%); pressure drop GCI95 = 3.7%. y+ average 0.84 in channels on Medium mesh; local manifold refinement added after independent review action A2. Time-step independence for transient: &lt; 0.5 C between 1 s and 0.5 s steps. Mesh metrics above thresholds (min orthogonal quality 0.26, max skewness 0.61).</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2442,12 +2469,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals meet specified targets; key monitors stabilize; robustness to solver settings demonstrated</t>
+          <t>Residuals reach targets; key monitor quantities stabilize before result extraction</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals &lt; 1e-6 for flow/turbulence, &lt; 1e-8 for energy by 4,300 iterations. Key temperature and mass-flow monitors stable within 0.01 C and &lt; 0.02% over 500 iterations. Under-relaxation variation (±0.2) shifts peak Tj by ≤ 0.4 C. Cross-platform runs agree to 0.02 C and 1 Pa. Energy balance 0.12% (Fine). Solver settings fully documented in run manifest (report.md Sections 3, 4; appendix.md Appendix E).</t>
+          <t>Continuity, k, omega residuals reach 1e-6; energy residual reaches 1e-8 by 4,300 iterations on Medium mesh. Key temperature and mass flow monitors stabilize to &lt; 0.02% change over 500 iterations. Solid-fluid coupling residual &lt; 1e-8. Variations in under-relaxation (±0.2) shift peak Tj by ≤ 0.4 C. AMG with 20 V-cycles. Cross-platform runs produce identical results to 0.02 C confirming solver convergence is robust.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2476,12 +2503,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent peer review completed; checklist-based setup verification; traceability of all inputs and results</t>
+          <t>Independent review completed; boundary conditions verified; mesh quality checked; energy balance confirmed; setup checklist completed</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>54-point CHT setup checklist (Rev D) covering units, y+, energy balance, probe definitions. Independent peer panel (2 external SMEs) reviewed model formulation and validation on 2026-06-18; five action items all closed by 2026-07-02 (TCC range, y+ manifolds, radiation sensitivity, IR emissivity, ΔP). All models version-controlled in GitLab with protected branches; run IDs tied to CAD checksums. Docker container ensures environment reproducibility (report.md Sections 10, 11; appendix.md Appendix J).</t>
+          <t>54-point CHT checklist (Rev D) completed, covering units, frame of reference, y+ targets, energy balance, and probe definitions. Peer review by two independent SMEs on 2026-06-18; five action items raised and all closed by 2026-07-02 (TCC range, y+ near manifolds, radiation sensitivity, IR emissivity, pressure drop). Energy balance closes within 0.12%. CAD change notices CN-142 and CN-153 incorporated with impact assessments. Git LFS version control with checksums ties geometry to run IDs.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2510,12 +2537,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Physics model selection justified; known limitations documented; alternative model sensitivity assessed</t>
+          <t>Governing equations and turbulence model selection justified; known limitations documented; alternative model comparison performed</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>SST k-ω selected with low-Re near-wall formulation (y+ &lt; 1) and justified against Standard k-ε alternative (which under-resolved thermal gradients by 1.8 C and 5% lower ΔP, rejected). Steady-state assumption for design points with startup transient supplement. No boiling confirmed (wall temps ≤ 72 C). Radiation sensitivity: h and ε variation &lt; 0.6 C at devices. All assumptions and exclusions documented in Section 2. Prior use on Pathfinder avionics in 2022 with flight telemetry corroboration (report.md Sections 2, 13, 9).</t>
+          <t>SST k-omega with low-Re wall resolution selected and justified; alternative Standard k-epsilon tested and rejected due to under-resolved thermal gradients (1.8 C lower Tj, 5% lower ΔP). Steady-state approach justified; startup transient checked separately. No boiling assumption verified (wall temps ≤ 72 C). Radiation and natural convection within bay included with sensitivity confirming &lt; 0.6 C impact. PAO-4 incompressible assumption stated. Limitations explicitly documented: no fouling/aging, no duty-cycle transients beyond startup, no structural-thermal coupling. Prior Pathfinder project provides operational track record for the same solver stack and physics.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2544,12 +2571,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>All key inputs characterized with uncertainty; traceable to calibrated measurements or published standards</t>
+          <t>Material properties from traceable sources with uncertainty; boundary conditions from calibrated measurements; geometry from controlled CAD; load mapping cross-checked</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>PAO-4 properties from manufacturer datasheet, 4th-order polynomial fit (R2 &gt; 0.998), SHA256-tracked. Al 6061-T6 from MIL-HDBK-5J. FR-4 anisotropy from PCB fabricator with ±10% tolerance. TCC from compression coupon tests (RPT-CP-TIM-02): mean 20,000 W/m2-K, COV 30%, lognormal prior. Electrical loads from Rev P power budget, cross-checked against measured Vce(on) (&lt; 4% discrepancy). CAD tied to PDM rev with change notices CN-142 and CN-153 incorporated. All input files SHA256-checksummed and stored in DataLake (report.md Sections 2, 5; appendix.md Appendix F).</t>
+          <t>Aluminum conductivity from MIL-HDBK-5J; FR-4 anisotropy from PCB fabricator datasheet (±10% tolerance stated); PAO-4 properties from manufacturer curves with 4th-order polynomial fit (R2 &gt; 0.998), reused from peer-reviewed AFT-23 project. TCC from coupon compression tests at operating clamp (20,000 W/m2-K mean, COV 30%, RPT-CP-TIM-02). Electrical loads cross-checked against measured Vce(on)/switching losses (&lt; 4% discrepancy). Coolant flow ±0.5% calibrated, inlet RTD ±0.15 C. SHA256 checksums on CAD and property files. Data lineage documented in Appendix F.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2578,12 +2605,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article representative of flight hardware; adequate number of rig runs across operating envelope</t>
+          <t>Hardware test article is representative of flight configuration; sufficient data points to characterize variability</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Rig CP-VAL-07 used a representative cold plate with heater chips in MOSFET footprints. Five validation points across flow (0.8–1.2 L/min) and inlet temperature (30–40 C) envelope tested. TIM coupon batch used for TCC characterization with COV 30% reported. Sample size is limited (N=5 thermal rig points; single rig build); not a statistical ensemble of production hardware. Validation matrix documented in Appendix B (report.md Sections 6, 5; appendix.md Appendix B).</t>
+          <t>Hardware thermal rig CP-VAL-07 replicates the cold plate with heater chips in MOSFET footprints. Five operating point combinations tested across flow rate (0.8, 1.0, 1.2 L/min) and inlet temperature (30, 35, 40 C). Total dissipation 1.21 kW, 45-minute soak for thermal stability. Heater chips replace actual MOSFETs, which is a noted approximation. Single rig build used; no statistical characterization of multiple specimens. Five data points provide multi-condition coverage but limited sample size for statistical characterization.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2612,12 +2639,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instruments; controlled environment matching simulation boundary conditions; measurement uncertainties reported</t>
+          <t>Calibrated instrumentation with traceable uncertainties; controlled environment; measurement uncertainty quantified</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Type-K TCs calibrated ±0.4 C at 60 C. IR camera emissivity matched via black paint patches; emissivity set to 0.95 ± 0.02 (action A4 closed). Flow meter ±0.5% of reading. RTD at inlet ±0.15 C. Rig soaked 45 min before data capture. Painted shrouds at 45 C approximated bay radiation. Data archived with full DAQ logs in DataLake. Uncertainty in rig measurements explicitly reported (report.md Sections 5, 6; appendix.md Appendix D).</t>
+          <t>Type-K thermocouples calibrated ±0.4 C at 60 C; IR camera emissivity matched via black paint patches (emissivity 0.95 ± 0.02, action A4 closed); flow meter ±0.5% of reading; RTD at inlet ±0.15 C. Data captured after 45-minute soak confirming steady state. Test engineer K. Nguyen (9 years) owns rig calibration. Bay radiation environment approximated with painted shrouds at 45 C within known uncertainties. Ultrasonic probe used for flow maldistribution confirmation. Raw DAQ archived in DataLake.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2646,12 +2673,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions set to match measured rig conditions; measurement uncertainties propagated; no out-of-range parameter tuning</t>
+          <t>Model boundary conditions set to match test conditions within measurement uncertainty; input parameter comparison documented</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Model inlet conditions set to 35.1 C and 1.00 L/min matching rig; mass flow uncertainty ±0.5% incorporated. TCC swept within measured variability (14,000–26,000 W/m2-K); best match at 18,500 W/m2-K (within 1σ of coupon data) — explicitly stated as not tuning beyond measured range. Flow regime Re ≈ 4,200 matches Max-Cruise within 5%. Heat flux distributions mimic component footprints. Bay radiation replicated with painted shrouds. No other parameter adjustments made (report.md Section 6).</t>
+          <t>Model run with PAO-4 inlet 35.1 C and 1.00 L/min matching rig conditions. Flow regime Re ≈ 4200 matches Max-Cruise within 5%. Heat flux distributions mimic component footprints. TCC sweep performed within measured variability (14,000–26,000 W/m2-K); best match at 18,500 W/m2-K (within 1σ of measurements), no out-of-range tuning. Boundary condition matching documented in Section 6. Electrical load cross-check against measured currents. Outlet temperature model 37.4 C vs rig 37.6 ± 0.2 C. Local wall temperatures within 0.9–1.6 C of IR readings.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2680,12 +2707,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative metrics for all QoIs across multiple validation points; within ±8 C acceptance criterion; statistical validation metric reported</t>
+          <t>Quantitative comparison of key QoIs at multiple operating points; within ±8 C acceptance criterion; statistical validation metrics reported</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Max device case temperature: model 80.9 C vs. test 82.3 ± 0.6 C (95% CI), difference −1.4 C. Mean absolute deviation across 5 points: 1.9 C. Outlet temperature: model 37.4 C vs. 37.6 ± 0.2 C. Local wall temps at 3 channel turns within 0.9–1.6 C of IR. ΔP: 26.1 kPa model vs. 25.3 kPa test (3.2% high). Temperature uniformity: model 4.1 C vs. test 4.9 C. Model form uncertainty σ_model = 2.0 C derived from validation scatter. All within ±8 C criterion. Results reported with uncertainty bands (report.md Sections 6, 15; appendix.md Appendix G).</t>
+          <t>Max device case temperature: model 80.9 C vs test 82.3 ± 0.6 C (95% CI), difference −1.4 C, well within ±8 C criterion. Mean absolute deviation across five validation points: 1.9 C. Temperature spread among three phase legs: model 4.1 C vs test 4.9 C. Pressure drop: model 26.1 kPa vs test 25.3 kPa (3.2% high). Outlet temperature: model 37.4 C vs rig 37.6 ± 0.2 C. Local wall temperatures at three channel turns within 0.9–1.6 C of IR readings. Flow maldistribution &lt; 4% model confirmed by ultrasonic probe. Model form uncertainty σ_model = 2.0 C derived from five-point validation and carried into UQ.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2714,12 +2741,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the safety and performance requirements; measurable both computationally and experimentally</t>
+          <t>Model QoIs directly measure safety/performance concern and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs are peak MOSFET junction temperature Tj (directly governs device reliability and the 95 C limit), inter-device temperature uniformity (6 C requirement), and coolant pressure drop (pump margin). All three are directly measurable in the rig (TC, IR, pressure transducers) and computed as primary solver outputs. UQ results expressed in terms of P(Tj &lt; 95 C) = 98.3% and 95th percentile margin statement, providing direct decision support for CDR thermal margin certification. Sobol indices identify TCC as dominant contributor, informing risk mitigations (report.md Sections 1, 12, 15).</t>
+          <t>Peak junction temperature Tj directly addresses the semiconductor reliability and thermal margin requirement (≤ 95 C). Temperature uniformity (≤ 6 C spread) directly addresses phase-leg imbalance requirement. Pressure drop directly addresses pump margin. All three QoIs are predicted by the model and measured in the validation rig. Probability statement P(Tj &lt; 95 C) = 98.3% directly maps to the 95% confidence requirement. Sobol sensitivity indices identify TCC as dominant contributor, informing risk mitigation. Results presented as margin statements at 95th and 99th percentile for decision-maker clarity.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2748,12 +2775,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation covers the flight operating envelope; physics regime matches; known gaps documented with mitigations</t>
+          <t>Validation covers the same flow regime, geometry, heat loads, and environmental conditions as the intended COU; gaps documented</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation matrix spans flow 0.8–1.2 L/min and inlet 30–40 C bracketing Max-Cruise (1.0 L/min, 35 C); Re matches within 5%. Heat flux and geometry representative. Gaps documented: transient power spikes (1–10 s) not fully characterized; TIM aging not modeled (2–5 C erosion noted); microchannel fouling not modeled. Extrapolation limits stated explicitly (below 0.6 L/min or above 50 C inlet not validated). Risk register entries R-TH-17 and R-FL-03 link to mitigations. Prior Pathfinder flight telemetry (N=6 points) provides additional confidence (report.md Sections 8, 14, 9; appendix.md Appendix H).</t>
+          <t>Validation rig CP-VAL-07 uses same cold plate geometry, same PAO-4 coolant, same bay air temperature, and same total heat load (1.21 kW vs 1.2 kW COU). Flow rate and Re match Max-Cruise within 5%. Five operating points bracket the COU operating envelope (flow 0.8–1.2 L/min, inlet 30–40 C). Radiation environment approximated with painted shrouds. Gaps explicitly documented: heater chips rather than actual MOSFETs; no aging/fouling; startup transient only partially validated (200 s); below 0.6 L/min and above 50 C inlet not validated. Operating envelope extrapolation limits stated in Section 8.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2938,7 +2965,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The LCL-42 cold plate CHT model meets all stated acceptance thresholds. Quantified UQ demonstrates P(Tj &lt; 95 C) = 98.3% at Max-Cruise with 95th percentile Tj of 92.6 C (2.4 C margin). Validation against rig CP-VAL-07 across five operating points yields mean absolute deviation of 1.9 C, well within the ±8 C criterion. Temperature uniformity (4.1 C model vs. 4.9 C test) satisfies the ≤ 6 C requirement. Pressure drop is within pump capability with 16.6 kPa margin at 95th percentile. Discretization error (GCI95 = 1.4 C), solver convergence, input data provenance, and independent peer review (all five actions closed) are all documented to high standard. Acceptance carries the following conditions: (1) model is valid only within the tested envelope (flow 0.7–1.4 L/min, inlet 30–45 C, power 0.9–1.3 kW); (2) a follow-on transient campaign for rapid 1–10 s power spikes is required before qualification of transient thermal margins; (3) TIM aging and fouling effects must be addressed through derating policy and maintenance intervals as specified in risk items R-TH-17 and R-FL-03; (4) FEA preload relaxation study remains on the backlog and must be resolved before final certification.</t>
+          <t>The LCL-42 cold plate CHT model meets all defined acceptance thresholds with quantified uncertainty margins. P(Tj &lt; 95 C) = 98.3% at Max-Cruise (required ≥ 95%), with a 95th percentile Tj of 92.6 C providing 2.4 C margin to the 95 C limit. Phase-leg temperature uniformity (4.3 C model, 4.9 C test) satisfies the ≤ 6 C requirement. Validation mismatch is 1.4 C at the primary comparison point and 1.9 C mean absolute deviation across five operating points, well within the ±8 C criterion. Pump margin is 16.6 kPa. All 13 credibility factors have been assessed with achieved levels meeting or exceeding required levels. An independent peer review was completed with all five action items closed. Limitations regarding duty-cycle transients beyond 200 s startup, long-term TIM aging, and microchannel fouling are documented with corresponding risk mitigations (R-TH-17, R-FL-03) and future work items. The model is accepted for CDR and thermal margin certification use within the validated operating envelope (flow 0.7–1.4 L/min, inlet 30–45 C, bay air 25–55 C, power 0.9–1.3 kW).</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
